--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.71422997329241</v>
+        <v>9.216062370660017</v>
       </c>
       <c r="D2" t="n">
-        <v>38.34017381063541</v>
+        <v>6.230278244228254</v>
       </c>
       <c r="E2" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F2" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.29567213677298</v>
+        <v>8.823046722225609</v>
       </c>
       <c r="D3" t="n">
-        <v>32.74814564343913</v>
+        <v>5.321573667058859</v>
       </c>
       <c r="E3" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F3" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.83476634246587</v>
+        <v>10.3731495306507</v>
       </c>
       <c r="D4" t="n">
-        <v>35.86748886344868</v>
+        <v>5.828466940310411</v>
       </c>
       <c r="E4" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F4" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.53782801935119</v>
+        <v>6.587397053144568</v>
       </c>
       <c r="D5" t="n">
-        <v>25.09660347881441</v>
+        <v>4.078198065307341</v>
       </c>
       <c r="E5" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F5" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.70677604933555</v>
+        <v>10.35235110801703</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39550714036059</v>
+        <v>6.076769910308596</v>
       </c>
       <c r="E6" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F6" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.10295124892754</v>
+        <v>9.604229577950726</v>
       </c>
       <c r="D7" t="n">
-        <v>48.09394741313898</v>
+        <v>7.815266454635085</v>
       </c>
       <c r="E7" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F7" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.04707988852692</v>
+        <v>6.020150481885625</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71566876732941</v>
+        <v>5.47879617469103</v>
       </c>
       <c r="E8" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F8" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.85697767712217</v>
+        <v>8.101758872532352</v>
       </c>
       <c r="D9" t="n">
-        <v>44.57132850303435</v>
+        <v>7.242840881743082</v>
       </c>
       <c r="E9" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F9" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>63.24030167847008</v>
+        <v>10.27654902275139</v>
       </c>
       <c r="D10" t="n">
-        <v>56.831418165509</v>
+        <v>9.235105451895214</v>
       </c>
       <c r="E10" t="n">
-        <v>9.398649237742122</v>
+        <v>1.527280501133095</v>
       </c>
       <c r="F10" t="n">
-        <v>8.847657826639473</v>
+        <v>1.437744396828915</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
